--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_TENEA-C.B. ESPARREGUERA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_TENEA-C.B. ESPARREGUERA.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>41.35939999999999</v>
+        <v>29.1427</v>
       </c>
       <c r="E2" t="n">
-        <v>24.6642</v>
+        <v>19.3825</v>
       </c>
       <c r="F2" t="n">
-        <v>16.695</v>
+        <v>9.7598</v>
       </c>
       <c r="G2" t="n">
         <v>-15.9395</v>
@@ -610,13 +610,13 @@
         <v>48.8359</v>
       </c>
       <c r="S2" t="n">
-        <v>20.8807</v>
+        <v>8.663600000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>5.9342</v>
+        <v>0.6524000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>14.9467</v>
+        <v>8.0115</v>
       </c>
       <c r="V2" t="n">
         <v>19.4236</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>11.4027</v>
+        <v>13.0751</v>
       </c>
       <c r="E3" t="n">
-        <v>16.9084</v>
+        <v>14.8681</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.5059</v>
+        <v>-1.793100000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>-22.0061</v>
+        <v>-4.530900000000002</v>
       </c>
       <c r="H3" t="n">
-        <v>-12.8222</v>
+        <v>-3.901399999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-9.1838</v>
+        <v>-0.6295999999999995</v>
       </c>
       <c r="J3" t="n">
-        <v>23.1235</v>
+        <v>30.0048</v>
       </c>
       <c r="K3" t="n">
-        <v>15.7014</v>
+        <v>22.6599</v>
       </c>
       <c r="L3" t="n">
-        <v>7.422</v>
+        <v>7.345200000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-45.1297</v>
+        <v>-34.536</v>
       </c>
       <c r="N3" t="n">
-        <v>-28.5235</v>
+        <v>-26.5613</v>
       </c>
       <c r="O3" t="n">
-        <v>-16.6059</v>
+        <v>-7.9746</v>
       </c>
       <c r="P3" t="n">
-        <v>5.2741</v>
+        <v>-14.4554</v>
       </c>
       <c r="Q3" t="n">
-        <v>-35.1616</v>
+        <v>-56.8447</v>
       </c>
       <c r="R3" t="n">
-        <v>40.436</v>
+        <v>42.3893</v>
       </c>
       <c r="S3" t="n">
-        <v>29.7526</v>
+        <v>-5.4204</v>
       </c>
       <c r="T3" t="n">
-        <v>26.5495</v>
+        <v>-3.6646</v>
       </c>
       <c r="U3" t="n">
-        <v>3.203</v>
+        <v>-1.7561</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.6181</v>
+        <v>37.4818</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3973</v>
+        <v>45.3722</v>
       </c>
       <c r="X3" t="n">
-        <v>-4.015099999999999</v>
+        <v>-7.8905</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. VERA CUSCOLL</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>5.6515</v>
+        <v>11.1354</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9418</v>
+        <v>11.1879</v>
       </c>
       <c r="F4" t="n">
-        <v>3.71</v>
+        <v>-0.05249999999999977</v>
       </c>
       <c r="G4" t="n">
-        <v>5.909</v>
+        <v>-0.6194999999999995</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3858</v>
+        <v>1.2387</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5231</v>
+        <v>-1.8583</v>
       </c>
       <c r="J4" t="n">
-        <v>6.6688</v>
+        <v>16.6593</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6032</v>
+        <v>16.6126</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0656</v>
+        <v>0.04629999999999979</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7596999999999999</v>
+        <v>-17.2787</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2174</v>
+        <v>-15.374</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5423000000000001</v>
+        <v>-1.9047</v>
       </c>
       <c r="P4" t="n">
-        <v>5.4695</v>
+        <v>15.4321</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.1021</v>
+        <v>-17.9714</v>
       </c>
       <c r="R4" t="n">
-        <v>9.5718</v>
+        <v>33.4035</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.1773</v>
+        <v>-0.8364999999999998</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.1207</v>
+        <v>1.3015</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0562</v>
+        <v>-2.1379</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.5499</v>
+        <v>-2.8408</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4958</v>
+        <v>11.1988</v>
       </c>
       <c r="X4" t="n">
-        <v>-4.0457</v>
+        <v>-14.0396</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>E. VERA CUSCOLL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>4.3553</v>
+        <v>8.312900000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>6.320399999999999</v>
+        <v>4.0037</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9655</v>
+        <v>4.3092</v>
       </c>
       <c r="G5" t="n">
-        <v>4.9966</v>
+        <v>5.909</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0764</v>
+        <v>3.3858</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9199</v>
+        <v>2.5231</v>
       </c>
       <c r="J5" t="n">
-        <v>12.0981</v>
+        <v>6.6688</v>
       </c>
       <c r="K5" t="n">
-        <v>8.901</v>
+        <v>3.6032</v>
       </c>
       <c r="L5" t="n">
-        <v>3.1969</v>
+        <v>3.0656</v>
       </c>
       <c r="M5" t="n">
-        <v>-7.1012</v>
+        <v>-0.7596999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-6.8247</v>
+        <v>-0.2174</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2766999999999998</v>
+        <v>-0.5423000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>1.758</v>
+        <v>5.4695</v>
       </c>
       <c r="Q5" t="n">
-        <v>-15.6273</v>
+        <v>-4.1021</v>
       </c>
       <c r="R5" t="n">
-        <v>17.3855</v>
+        <v>9.5718</v>
       </c>
       <c r="S5" t="n">
-        <v>8.526200000000001</v>
+        <v>-0.5161</v>
       </c>
       <c r="T5" t="n">
-        <v>8.131600000000001</v>
+        <v>-0.05880000000000003</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3944000000000001</v>
+        <v>-0.4572999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-10.9256</v>
+        <v>-2.5499</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7181</v>
+        <v>1.4958</v>
       </c>
       <c r="X5" t="n">
-        <v>-12.6437</v>
+        <v>-4.0457</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7379</v>
+        <v>4.492000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>6.8024</v>
+        <v>5.0405</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.0644</v>
+        <v>-0.5486000000000004</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6194999999999995</v>
+        <v>-10.3176</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2387</v>
+        <v>-8.6417</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.8583</v>
+        <v>-1.6758</v>
       </c>
       <c r="J6" t="n">
-        <v>16.6593</v>
+        <v>15.5526</v>
       </c>
       <c r="K6" t="n">
-        <v>16.6126</v>
+        <v>13.031</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04629999999999979</v>
+        <v>2.5217</v>
       </c>
       <c r="M6" t="n">
-        <v>-17.2787</v>
+        <v>-25.8705</v>
       </c>
       <c r="N6" t="n">
-        <v>-15.374</v>
+        <v>-21.6727</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.9047</v>
+        <v>-4.1975</v>
       </c>
       <c r="P6" t="n">
-        <v>15.4321</v>
+        <v>4.492999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>-17.9714</v>
+        <v>-41.0218</v>
       </c>
       <c r="R6" t="n">
-        <v>33.4035</v>
+        <v>45.5149</v>
       </c>
       <c r="S6" t="n">
-        <v>-9.2338</v>
+        <v>3.0847</v>
       </c>
       <c r="T6" t="n">
-        <v>-3.0841</v>
+        <v>2.4755</v>
       </c>
       <c r="U6" t="n">
-        <v>-6.1496</v>
+        <v>0.6091999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.8408</v>
+        <v>7.231899999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>11.1988</v>
+        <v>28.0344</v>
       </c>
       <c r="X6" t="n">
-        <v>-14.0396</v>
+        <v>-20.8022</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5524</v>
+        <v>1.823</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3732</v>
+        <v>0.5348999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1793</v>
+        <v>1.2882</v>
       </c>
       <c r="G7" t="n">
         <v>1.0148</v>
@@ -1000,13 +1000,13 @@
         <v>0.7813</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2438</v>
+        <v>0.02689999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.242</v>
+        <v>-0.0804</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.001599999999999997</v>
+        <v>0.1073</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9195</v>
+        <v>1.2681</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5787</v>
+        <v>-0.1743</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4982</v>
+        <v>1.4424</v>
       </c>
       <c r="G8" t="n">
         <v>1.6071</v>
@@ -1078,13 +1078,13 @@
         <v>0.7814</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0269</v>
+        <v>0.3756</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.4429</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8742</v>
+        <v>0.8184</v>
       </c>
       <c r="V8" t="n">
         <v>-1.4959</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. SANCHO GERVÁS</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5384</v>
+        <v>-0.3855999999999997</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0701</v>
+        <v>1.3646</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6085</v>
+        <v>-1.7499</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0129</v>
+        <v>4.9966</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0663</v>
+        <v>2.0764</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0792</v>
+        <v>2.9199</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0013</v>
+        <v>12.0981</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0013</v>
+        <v>8.901</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.1969</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0142</v>
+        <v>-7.1012</v>
       </c>
       <c r="N9" t="n">
-        <v>0.065</v>
+        <v>-6.8247</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0792</v>
+        <v>-0.2766999999999998</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1953</v>
+        <v>1.758</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-15.6273</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7814</v>
+        <v>17.3855</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9471000000000001</v>
+        <v>3.7856</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0456</v>
+        <v>3.1759</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0985</v>
+        <v>0.6098000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2772</v>
+        <v>-10.9256</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.7181</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2772</v>
+        <v>-12.6437</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9823999999999997</v>
+        <v>-1.236</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8099</v>
+        <v>-3.2262</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8273000000000001</v>
+        <v>1.9904</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6702</v>
@@ -1234,13 +1234,13 @@
         <v>12.1111</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3386999999999999</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>1.7647</v>
+        <v>0.3484</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.1034</v>
+        <v>-0.9405999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>-0.7317</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>F. SANCHO GERVÁS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2347</v>
+        <v>-1.2928</v>
       </c>
       <c r="E11" t="n">
-        <v>2.535600000000001</v>
+        <v>-0.7388</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.7703</v>
+        <v>-0.5541</v>
       </c>
       <c r="G11" t="n">
-        <v>-10.3176</v>
+        <v>-1.0129</v>
       </c>
       <c r="H11" t="n">
-        <v>-8.6417</v>
+        <v>0.0663</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.6758</v>
+        <v>-1.0792</v>
       </c>
       <c r="J11" t="n">
-        <v>15.5526</v>
+        <v>0.0013</v>
       </c>
       <c r="K11" t="n">
-        <v>13.031</v>
+        <v>0.0013</v>
       </c>
       <c r="L11" t="n">
-        <v>2.5217</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-25.8705</v>
+        <v>-1.0142</v>
       </c>
       <c r="N11" t="n">
-        <v>-21.6727</v>
+        <v>0.065</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.1975</v>
+        <v>-1.0792</v>
       </c>
       <c r="P11" t="n">
-        <v>4.492999999999999</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q11" t="n">
-        <v>-41.0218</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>45.5149</v>
+        <v>0.7814</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.642199999999999</v>
+        <v>0.1926</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.02969999999999984</v>
+        <v>0.2367</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.6129</v>
+        <v>-0.044</v>
       </c>
       <c r="V11" t="n">
-        <v>7.231899999999999</v>
+        <v>-0.2772</v>
       </c>
       <c r="W11" t="n">
-        <v>28.0344</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-20.8022</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>I. EXPOSITO CORTS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0849</v>
+        <v>-3.5008</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.8708</v>
+        <v>-4.4606</v>
       </c>
       <c r="F12" t="n">
-        <v>3.7862</v>
+        <v>0.9597000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.061000000000001</v>
+        <v>-2.6107</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.9538</v>
+        <v>1.7985</v>
       </c>
       <c r="I12" t="n">
-        <v>2.893</v>
+        <v>-4.4091</v>
       </c>
       <c r="J12" t="n">
-        <v>5.4838</v>
+        <v>-2.9399</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4491</v>
+        <v>1.0642</v>
       </c>
       <c r="L12" t="n">
-        <v>3.0348</v>
+        <v>-4.0041</v>
       </c>
       <c r="M12" t="n">
-        <v>-7.5449</v>
+        <v>0.3292</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.403</v>
+        <v>0.7342</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1420999999999997</v>
+        <v>-0.405</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5392</v>
+        <v>-0.1954</v>
       </c>
       <c r="Q12" t="n">
-        <v>-16.7993</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>19.3388</v>
+        <v>0.7813</v>
       </c>
       <c r="S12" t="n">
-        <v>7.5684</v>
+        <v>-0.4175</v>
       </c>
       <c r="T12" t="n">
-        <v>7.317600000000001</v>
+        <v>-0.5438999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2509999999999999</v>
+        <v>0.1264</v>
       </c>
       <c r="V12" t="n">
-        <v>-11.1321</v>
+        <v>-0.2772</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.8732</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.2591</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I. EXPOSITO CORTS</t>
+          <t>P. ROIG GARCIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.0221</v>
+        <v>-5.6431</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.763999999999999</v>
+        <v>-7.3098</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7419000000000001</v>
+        <v>1.6668</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.6107</v>
+        <v>-7.0146</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7985</v>
+        <v>-3.7908</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.4091</v>
+        <v>-3.2239</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.9399</v>
+        <v>-4.3317</v>
       </c>
       <c r="K13" t="n">
-        <v>1.0642</v>
+        <v>-2.9984</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.0041</v>
+        <v>-1.3333</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3292</v>
+        <v>-2.6829</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7342</v>
+        <v>-0.7924</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.405</v>
+        <v>-1.8905</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1954</v>
+        <v>1.5627</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>-3.1255</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7813</v>
+        <v>4.6882</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9387000000000001</v>
+        <v>0.03180000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8472999999999999</v>
+        <v>-1.0712</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.09140000000000001</v>
+        <v>1.103</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2772</v>
+        <v>-0.2228999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2772</v>
+        <v>-1.4415</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>S. ROMEO FO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.844499999999999</v>
+        <v>-6.880800000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3621</v>
+        <v>-5.392300000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.207100000000001</v>
+        <v>-1.4886</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.530900000000002</v>
+        <v>-4.241200000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.901399999999999</v>
+        <v>-0.8161000000000003</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6295999999999995</v>
+        <v>-3.4252</v>
       </c>
       <c r="J14" t="n">
-        <v>30.0048</v>
+        <v>1.9592</v>
       </c>
       <c r="K14" t="n">
-        <v>22.6599</v>
+        <v>0.2558</v>
       </c>
       <c r="L14" t="n">
-        <v>7.345200000000001</v>
+        <v>1.7036</v>
       </c>
       <c r="M14" t="n">
-        <v>-34.536</v>
+        <v>-6.2004</v>
       </c>
       <c r="N14" t="n">
-        <v>-26.5613</v>
+        <v>-1.0721</v>
       </c>
       <c r="O14" t="n">
-        <v>-7.9746</v>
+        <v>-5.1287</v>
       </c>
       <c r="P14" t="n">
-        <v>-14.4554</v>
+        <v>1.5629</v>
       </c>
       <c r="Q14" t="n">
-        <v>-56.8447</v>
+        <v>-7.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>42.3893</v>
+        <v>8.7905</v>
       </c>
       <c r="S14" t="n">
-        <v>-25.3404</v>
+        <v>-0.9671</v>
       </c>
       <c r="T14" t="n">
-        <v>-17.1705</v>
+        <v>-0.4011</v>
       </c>
       <c r="U14" t="n">
-        <v>-8.169599999999999</v>
+        <v>-0.5660000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>37.4818</v>
+        <v>-3.2354</v>
       </c>
       <c r="W14" t="n">
-        <v>45.3722</v>
+        <v>0.2772</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.8905</v>
+        <v>-3.5126</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. ROMEO FO</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>-7.882099999999999</v>
+        <v>-9.1099</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.5039</v>
+        <v>-1.982299999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3783</v>
+        <v>-7.127400000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-4.241200000000001</v>
+        <v>-22.0061</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8161000000000003</v>
+        <v>-12.8222</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.4252</v>
+        <v>-9.1838</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9592</v>
+        <v>23.1235</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2558</v>
+        <v>15.7014</v>
       </c>
       <c r="L15" t="n">
-        <v>1.7036</v>
+        <v>7.422</v>
       </c>
       <c r="M15" t="n">
-        <v>-6.2004</v>
+        <v>-45.1297</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0721</v>
+        <v>-28.5235</v>
       </c>
       <c r="O15" t="n">
-        <v>-5.1287</v>
+        <v>-16.6059</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5629</v>
+        <v>5.2741</v>
       </c>
       <c r="Q15" t="n">
-        <v>-7.2276</v>
+        <v>-35.1616</v>
       </c>
       <c r="R15" t="n">
-        <v>8.7905</v>
+        <v>40.436</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.968</v>
+        <v>9.239800000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.5125</v>
+        <v>7.658799999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4555000000000001</v>
+        <v>1.5814</v>
       </c>
       <c r="V15" t="n">
-        <v>-3.2354</v>
+        <v>-1.6181</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2772</v>
+        <v>2.3973</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.5126</v>
+        <v>-4.015099999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. ROIG GARCIA</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D16" t="n">
-        <v>-8.2835</v>
+        <v>-9.250999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-9.1904</v>
+        <v>-12.4338</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9069</v>
+        <v>3.183</v>
       </c>
       <c r="G16" t="n">
-        <v>-7.0146</v>
+        <v>-2.061000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.7908</v>
+        <v>-4.9538</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.2239</v>
+        <v>2.893</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.3317</v>
+        <v>5.4838</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.9984</v>
+        <v>2.4491</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.3333</v>
+        <v>3.0348</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.6829</v>
+        <v>-7.5449</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7924</v>
+        <v>-7.403</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8905</v>
+        <v>-0.1420999999999997</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5627</v>
+        <v>2.5392</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.1255</v>
+        <v>-16.7993</v>
       </c>
       <c r="R16" t="n">
-        <v>4.6882</v>
+        <v>19.3388</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.6088</v>
+        <v>1.4025</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.9519</v>
+        <v>1.7545</v>
       </c>
       <c r="U16" t="n">
-        <v>0.343</v>
+        <v>-0.3522</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2228999999999999</v>
+        <v>-11.1321</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2186</v>
+        <v>-2.8732</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4415</v>
+        <v>-8.2591</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>-15.0368</v>
+        <v>-12.0611</v>
       </c>
       <c r="E17" t="n">
-        <v>-8.0677</v>
+        <v>-5.824800000000002</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.9691</v>
+        <v>-6.2364</v>
       </c>
       <c r="G17" t="n">
         <v>-15.2057</v>
@@ -1780,13 +1780,13 @@
         <v>14.0647</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8702</v>
+        <v>1.1054</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4390999999999997</v>
+        <v>1.8039</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.431</v>
+        <v>-0.6983</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1096999999999997</v>
@@ -1813,13 +1813,13 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>-20.7955</v>
+        <v>-15.2861</v>
       </c>
       <c r="E18" t="n">
-        <v>-10.9644</v>
+        <v>-6.618200000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-9.831199999999999</v>
+        <v>-8.668000000000001</v>
       </c>
       <c r="G18" t="n">
         <v>-14.3432</v>
@@ -1858,13 +1858,13 @@
         <v>20.9016</v>
       </c>
       <c r="S18" t="n">
-        <v>-8.260300000000001</v>
+        <v>-2.7508</v>
       </c>
       <c r="T18" t="n">
-        <v>-6.6316</v>
+        <v>-2.2853</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.6284</v>
+        <v>-0.4655</v>
       </c>
       <c r="V18" t="n">
         <v>-10.3035</v>
@@ -1891,13 +1891,13 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>-42.0012</v>
+        <v>-31.021</v>
       </c>
       <c r="E19" t="n">
-        <v>-29.3011</v>
+        <v>-20.8906</v>
       </c>
       <c r="F19" t="n">
-        <v>-12.7003</v>
+        <v>-10.1306</v>
       </c>
       <c r="G19" t="n">
         <v>-41.5021</v>
@@ -1936,13 +1936,13 @@
         <v>41.2174</v>
       </c>
       <c r="S19" t="n">
-        <v>-15.6275</v>
+        <v>-4.6473</v>
       </c>
       <c r="T19" t="n">
-        <v>-10.7986</v>
+        <v>-2.3882</v>
       </c>
       <c r="U19" t="n">
-        <v>-4.8292</v>
+        <v>-2.2591</v>
       </c>
       <c r="V19" t="n">
         <v>21.7698</v>
@@ -1969,13 +1969,13 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-46.8951</v>
+        <v>-37.1445</v>
       </c>
       <c r="E20" t="n">
-        <v>-26.7559</v>
+        <v>-19.256</v>
       </c>
       <c r="F20" t="n">
-        <v>-20.1393</v>
+        <v>-17.8887</v>
       </c>
       <c r="G20" t="n">
         <v>-20.7016</v>
@@ -2014,13 +2014,13 @@
         <v>32.8177</v>
       </c>
       <c r="S20" t="n">
-        <v>-12.7557</v>
+        <v>-3.0054</v>
       </c>
       <c r="T20" t="n">
-        <v>-9.2469</v>
+        <v>-1.7474</v>
       </c>
       <c r="U20" t="n">
-        <v>-3.5089</v>
+        <v>-1.2577</v>
       </c>
       <c r="V20" t="n">
         <v>-9.1401</v>
@@ -2047,19 +2047,19 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>-89.6225</v>
+        <v>-63.5635</v>
       </c>
       <c r="E21" t="n">
-        <v>-43.82859999999999</v>
+        <v>-31.9255</v>
       </c>
       <c r="F21" t="n">
-        <v>-45.7951</v>
+        <v>-31.6384</v>
       </c>
       <c r="G21" t="n">
         <v>-150.2493</v>
       </c>
       <c r="H21" t="n">
-        <v>-68.627</v>
+        <v>-68.62700000000001</v>
       </c>
       <c r="I21" t="n">
         <v>-81.6216</v>
@@ -2086,19 +2086,19 @@
         <v>46.8823</v>
       </c>
       <c r="Q21" t="n">
-        <v>-347.7083000000001</v>
+        <v>-347.7083</v>
       </c>
       <c r="R21" t="n">
         <v>394.5923</v>
       </c>
       <c r="S21" t="n">
-        <v>-17.3035</v>
+        <v>8.755199999999997</v>
       </c>
       <c r="T21" t="n">
-        <v>-5.178999999999998</v>
+        <v>6.7238</v>
       </c>
       <c r="U21" t="n">
-        <v>-12.1239</v>
+        <v>2.032299999999999</v>
       </c>
       <c r="V21" t="n">
         <v>31.047</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_TENEA-C.B. ESPARREGUERA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_TENEA-C.B. ESPARREGUERA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:X24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>13.0751</v>
+        <v>20.4218</v>
       </c>
       <c r="E3" t="n">
-        <v>14.8681</v>
+        <v>20.4218</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.793100000000001</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.530900000000002</v>
+        <v>20.4218</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.901399999999999</v>
+        <v>7.6749</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6295999999999995</v>
+        <v>12.7469</v>
       </c>
       <c r="J3" t="n">
-        <v>30.0048</v>
+        <v>20.4218</v>
       </c>
       <c r="K3" t="n">
-        <v>22.6599</v>
+        <v>7.6749</v>
       </c>
       <c r="L3" t="n">
-        <v>7.345200000000001</v>
+        <v>12.7469</v>
       </c>
       <c r="M3" t="n">
-        <v>-34.536</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-26.5613</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-7.9746</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-14.4554</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-56.8447</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>42.3893</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-5.4204</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-3.6646</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.7561</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>37.4818</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>45.3722</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-7.8905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>11.1354</v>
+        <v>13.0751</v>
       </c>
       <c r="E4" t="n">
-        <v>11.1879</v>
+        <v>14.8681</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.05249999999999977</v>
+        <v>-1.793100000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6194999999999995</v>
+        <v>-4.530900000000002</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2387</v>
+        <v>-3.901399999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.8583</v>
+        <v>-0.6295999999999995</v>
       </c>
       <c r="J4" t="n">
-        <v>16.6593</v>
+        <v>30.0048</v>
       </c>
       <c r="K4" t="n">
-        <v>16.6126</v>
+        <v>22.6599</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04629999999999979</v>
+        <v>7.345200000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-17.2787</v>
+        <v>-34.536</v>
       </c>
       <c r="N4" t="n">
-        <v>-15.374</v>
+        <v>-26.5613</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.9047</v>
+        <v>-7.9746</v>
       </c>
       <c r="P4" t="n">
-        <v>15.4321</v>
+        <v>-14.4554</v>
       </c>
       <c r="Q4" t="n">
-        <v>-17.9714</v>
+        <v>-56.8447</v>
       </c>
       <c r="R4" t="n">
-        <v>33.4035</v>
+        <v>42.3893</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8364999999999998</v>
+        <v>-5.4204</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3015</v>
+        <v>-3.6646</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.1379</v>
+        <v>-1.7561</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.8408</v>
+        <v>37.4818</v>
       </c>
       <c r="W4" t="n">
-        <v>11.1988</v>
+        <v>45.3722</v>
       </c>
       <c r="X4" t="n">
-        <v>-14.0396</v>
+        <v>-7.8905</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. VERA CUSCOLL</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>8.312900000000001</v>
+        <v>11.1354</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0037</v>
+        <v>11.1879</v>
       </c>
       <c r="F5" t="n">
-        <v>4.3092</v>
+        <v>-0.05249999999999977</v>
       </c>
       <c r="G5" t="n">
-        <v>5.909</v>
+        <v>-0.6194999999999995</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3858</v>
+        <v>1.2387</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5231</v>
+        <v>-1.8583</v>
       </c>
       <c r="J5" t="n">
-        <v>6.6688</v>
+        <v>16.6593</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6032</v>
+        <v>16.6126</v>
       </c>
       <c r="L5" t="n">
-        <v>3.0656</v>
+        <v>0.04629999999999979</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7596999999999999</v>
+        <v>-17.2787</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2174</v>
+        <v>-15.374</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5423000000000001</v>
+        <v>-1.9047</v>
       </c>
       <c r="P5" t="n">
-        <v>5.4695</v>
+        <v>15.4321</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.1021</v>
+        <v>-17.9714</v>
       </c>
       <c r="R5" t="n">
-        <v>9.5718</v>
+        <v>33.4035</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5161</v>
+        <v>-0.8364999999999998</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.05880000000000003</v>
+        <v>1.3015</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4572999999999999</v>
+        <v>-2.1379</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.5499</v>
+        <v>-2.8408</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4958</v>
+        <v>11.1988</v>
       </c>
       <c r="X5" t="n">
-        <v>-4.0457</v>
+        <v>-14.0396</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>E. VERA CUSCOLL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>4.492000000000001</v>
+        <v>8.312900000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>5.0405</v>
+        <v>4.0037</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5486000000000004</v>
+        <v>4.3092</v>
       </c>
       <c r="G6" t="n">
-        <v>-10.3176</v>
+        <v>5.909</v>
       </c>
       <c r="H6" t="n">
-        <v>-8.6417</v>
+        <v>3.3858</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6758</v>
+        <v>2.5231</v>
       </c>
       <c r="J6" t="n">
-        <v>15.5526</v>
+        <v>6.6688</v>
       </c>
       <c r="K6" t="n">
-        <v>13.031</v>
+        <v>3.6032</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5217</v>
+        <v>3.0656</v>
       </c>
       <c r="M6" t="n">
-        <v>-25.8705</v>
+        <v>-0.7596999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-21.6727</v>
+        <v>-0.2174</v>
       </c>
       <c r="O6" t="n">
-        <v>-4.1975</v>
+        <v>-0.5423000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>4.492999999999999</v>
+        <v>5.4695</v>
       </c>
       <c r="Q6" t="n">
-        <v>-41.0218</v>
+        <v>-4.1021</v>
       </c>
       <c r="R6" t="n">
-        <v>45.5149</v>
+        <v>9.5718</v>
       </c>
       <c r="S6" t="n">
-        <v>3.0847</v>
+        <v>-0.5161</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4755</v>
+        <v>-0.05880000000000003</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6091999999999999</v>
+        <v>-0.4572999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>7.231899999999999</v>
+        <v>-2.5499</v>
       </c>
       <c r="W6" t="n">
-        <v>28.0344</v>
+        <v>1.4958</v>
       </c>
       <c r="X6" t="n">
-        <v>-20.8022</v>
+        <v>-4.0457</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. TORRALBA CAROZ</t>
+          <t>M. SELLARÈS GIRALT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,61 +952,61 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.823</v>
+        <v>3.356</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5348999999999999</v>
+        <v>3.356</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2882</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0148</v>
+        <v>3.356</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3407</v>
+        <v>1.535</v>
       </c>
       <c r="I7" t="n">
-        <v>0.674</v>
+        <v>1.821</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6153</v>
+        <v>3.356</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6153</v>
+        <v>1.535</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.821</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3996</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2746</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.674</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7813</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7813</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.02689999999999999</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0804</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1073</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MERI RIUS</t>
+          <t>D. TORRALBA CAROZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2681</v>
+        <v>1.823</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1743</v>
+        <v>0.5348999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4424</v>
+        <v>1.2882</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6071</v>
+        <v>1.0148</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3937</v>
+        <v>0.3407</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2134</v>
+        <v>0.674</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2686</v>
+        <v>0.6153</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2686</v>
+        <v>0.6153</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.3385</v>
+        <v>0.3996</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1251</v>
+        <v>-0.2746</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2134</v>
+        <v>0.674</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7814</v>
+        <v>0.7813</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7814</v>
+        <v>0.7813</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3756</v>
+        <v>0.02689999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4429</v>
+        <v>-0.0804</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8184</v>
+        <v>0.1073</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>Q. BARDÉS BADIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3855999999999997</v>
+        <v>1.535</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3646</v>
+        <v>1.535</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7499</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>4.9966</v>
+        <v>1.535</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0764</v>
+        <v>1.535</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9199</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>12.0981</v>
+        <v>1.535</v>
       </c>
       <c r="K9" t="n">
-        <v>8.901</v>
+        <v>1.535</v>
       </c>
       <c r="L9" t="n">
-        <v>3.1969</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-7.1012</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-6.8247</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2766999999999998</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.758</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-15.6273</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>17.3855</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.7856</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.1759</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6098000000000001</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-10.9256</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7181</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-12.6437</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. SELLARÈS GIRALT</t>
+          <t>A. MERI RIUS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.236</v>
+        <v>1.2681</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2262</v>
+        <v>-0.1743</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9904</v>
+        <v>1.4424</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6702</v>
+        <v>1.6071</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7471</v>
+        <v>0.3937</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.4174</v>
+        <v>1.2134</v>
       </c>
       <c r="J10" t="n">
-        <v>5.4472</v>
+        <v>0.2686</v>
       </c>
       <c r="K10" t="n">
-        <v>5.7009</v>
+        <v>0.2686</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.2537000000000004</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-7.117599999999999</v>
+        <v>1.3385</v>
       </c>
       <c r="N10" t="n">
-        <v>-4.9535</v>
+        <v>0.1251</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.1639</v>
+        <v>1.2134</v>
       </c>
       <c r="P10" t="n">
-        <v>1.758</v>
+        <v>0.7814</v>
       </c>
       <c r="Q10" t="n">
-        <v>-10.353</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>12.1111</v>
+        <v>0.7814</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.3756</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3484</v>
+        <v>-0.4429</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9405999999999999</v>
+        <v>0.8184</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7317</v>
+        <v>-1.4959</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3313</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.0628</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. SANCHO GERVÁS</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2928</v>
+        <v>-0.3855999999999997</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7388</v>
+        <v>1.3646</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5541</v>
+        <v>-1.7499</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0129</v>
+        <v>4.9966</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0663</v>
+        <v>2.0764</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0792</v>
+        <v>2.9199</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0013</v>
+        <v>12.0981</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0013</v>
+        <v>8.901</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.1969</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0142</v>
+        <v>-7.1012</v>
       </c>
       <c r="N11" t="n">
-        <v>0.065</v>
+        <v>-6.8247</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0792</v>
+        <v>-0.2766999999999998</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1953</v>
+        <v>1.758</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>-15.6273</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7814</v>
+        <v>17.3855</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1926</v>
+        <v>3.7856</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2367</v>
+        <v>3.1759</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.044</v>
+        <v>0.6098000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2772</v>
+        <v>-10.9256</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.7181</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2772</v>
+        <v>-12.6437</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. EXPOSITO CORTS</t>
+          <t>F. SANCHO GERVAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,61 +1342,61 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5008</v>
+        <v>-1.2928</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4606</v>
+        <v>-0.7388</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9597000000000001</v>
+        <v>-0.5541</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.6107</v>
+        <v>-1.0129</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7985</v>
+        <v>0.0663</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.4091</v>
+        <v>-1.0792</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.9399</v>
+        <v>0.0013</v>
       </c>
       <c r="K12" t="n">
-        <v>1.0642</v>
+        <v>0.0013</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.0041</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3292</v>
+        <v>-1.0142</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7342</v>
+        <v>0.065</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.405</v>
+        <v>-1.0792</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1954</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7813</v>
+        <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4175</v>
+        <v>0.1926</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5438999999999999</v>
+        <v>0.2367</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1264</v>
+        <v>-0.044</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2772</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. ROIG GARCIA</t>
+          <t>I. EXPOSITO CORTS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.6431</v>
+        <v>-3.5008</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.3098</v>
+        <v>-4.4606</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6668</v>
+        <v>0.9597000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.0146</v>
+        <v>-2.6107</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.7908</v>
+        <v>1.7985</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.2239</v>
+        <v>-4.4091</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.3317</v>
+        <v>-2.9399</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.9984</v>
+        <v>1.0642</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.3333</v>
+        <v>-4.0041</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.6829</v>
+        <v>0.3292</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7924</v>
+        <v>0.7342</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.8905</v>
+        <v>-0.405</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5627</v>
+        <v>-0.1954</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.1255</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>4.6882</v>
+        <v>0.7813</v>
       </c>
       <c r="S13" t="n">
-        <v>0.03180000000000001</v>
+        <v>-0.4175</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0712</v>
+        <v>-0.5438999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>1.103</v>
+        <v>0.1264</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2228999999999999</v>
+        <v>-0.2772</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.4415</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. ROMEO FO</t>
+          <t>M. SELLARES GIRALT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.880800000000001</v>
+        <v>-4.591699999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.392300000000001</v>
+        <v>-6.582100000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4886</v>
+        <v>1.9904</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.241200000000001</v>
+        <v>-5.026199999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8161000000000003</v>
+        <v>-0.7876000000000003</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.4252</v>
+        <v>-4.2384</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9592</v>
+        <v>2.0913</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2558</v>
+        <v>4.165900000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>1.7036</v>
+        <v>-2.0745</v>
       </c>
       <c r="M14" t="n">
-        <v>-6.2004</v>
+        <v>-7.117599999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0721</v>
+        <v>-4.9535</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.1287</v>
+        <v>-2.1639</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5629</v>
+        <v>1.758</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.2276</v>
+        <v>-10.353</v>
       </c>
       <c r="R14" t="n">
-        <v>8.7905</v>
+        <v>12.1111</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9671</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4011</v>
+        <v>0.3484</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5660000000000001</v>
+        <v>-0.9405999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.2354</v>
+        <v>-0.7317</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2772</v>
+        <v>1.3313</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.5126</v>
+        <v>-2.0628</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>P. ROIG GARCIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>-9.1099</v>
+        <v>-5.6431</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.982299999999999</v>
+        <v>-7.3098</v>
       </c>
       <c r="F15" t="n">
-        <v>-7.127400000000001</v>
+        <v>1.6668</v>
       </c>
       <c r="G15" t="n">
-        <v>-22.0061</v>
+        <v>-7.0146</v>
       </c>
       <c r="H15" t="n">
-        <v>-12.8222</v>
+        <v>-3.7908</v>
       </c>
       <c r="I15" t="n">
-        <v>-9.1838</v>
+        <v>-3.2239</v>
       </c>
       <c r="J15" t="n">
-        <v>23.1235</v>
+        <v>-4.3317</v>
       </c>
       <c r="K15" t="n">
-        <v>15.7014</v>
+        <v>-2.9984</v>
       </c>
       <c r="L15" t="n">
-        <v>7.422</v>
+        <v>-1.3333</v>
       </c>
       <c r="M15" t="n">
-        <v>-45.1297</v>
+        <v>-2.6829</v>
       </c>
       <c r="N15" t="n">
-        <v>-28.5235</v>
+        <v>-0.7924</v>
       </c>
       <c r="O15" t="n">
-        <v>-16.6059</v>
+        <v>-1.8905</v>
       </c>
       <c r="P15" t="n">
-        <v>5.2741</v>
+        <v>1.5627</v>
       </c>
       <c r="Q15" t="n">
-        <v>-35.1616</v>
+        <v>-3.1255</v>
       </c>
       <c r="R15" t="n">
-        <v>40.436</v>
+        <v>4.6882</v>
       </c>
       <c r="S15" t="n">
-        <v>9.239800000000001</v>
+        <v>0.03180000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>7.658799999999999</v>
+        <v>-1.0712</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5814</v>
+        <v>1.103</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.6181</v>
+        <v>-0.2228999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3973</v>
+        <v>1.2186</v>
       </c>
       <c r="X15" t="n">
-        <v>-4.015099999999999</v>
+        <v>-1.4415</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>S. ROMEO FO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>-9.250999999999999</v>
+        <v>-6.880800000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-12.4338</v>
+        <v>-5.392300000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>3.183</v>
+        <v>-1.4886</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.061000000000001</v>
+        <v>-4.241200000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>-4.9538</v>
+        <v>-0.8161000000000003</v>
       </c>
       <c r="I16" t="n">
-        <v>2.893</v>
+        <v>-3.4252</v>
       </c>
       <c r="J16" t="n">
-        <v>5.4838</v>
+        <v>1.9592</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4491</v>
+        <v>0.2558</v>
       </c>
       <c r="L16" t="n">
-        <v>3.0348</v>
+        <v>1.7036</v>
       </c>
       <c r="M16" t="n">
-        <v>-7.5449</v>
+        <v>-6.2004</v>
       </c>
       <c r="N16" t="n">
-        <v>-7.403</v>
+        <v>-1.0721</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1420999999999997</v>
+        <v>-5.1287</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5392</v>
+        <v>1.5629</v>
       </c>
       <c r="Q16" t="n">
-        <v>-16.7993</v>
+        <v>-7.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>19.3388</v>
+        <v>8.7905</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4025</v>
+        <v>-0.9671</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7545</v>
+        <v>-0.4011</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3522</v>
+        <v>-0.5660000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-11.1321</v>
+        <v>-3.2354</v>
       </c>
       <c r="W16" t="n">
-        <v>-2.8732</v>
+        <v>0.2772</v>
       </c>
       <c r="X16" t="n">
-        <v>-8.2591</v>
+        <v>-3.5126</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Q. ROIG GARCIA</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>-12.0611</v>
+        <v>-9.1099</v>
       </c>
       <c r="E17" t="n">
-        <v>-5.824800000000002</v>
+        <v>-1.982299999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.2364</v>
+        <v>-7.127400000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-15.2057</v>
+        <v>-22.0061</v>
       </c>
       <c r="H17" t="n">
-        <v>-6.1851</v>
+        <v>-12.8222</v>
       </c>
       <c r="I17" t="n">
-        <v>-9.0207</v>
+        <v>-9.1838</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.8089</v>
+        <v>23.1235</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1381</v>
+        <v>15.7014</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.9471</v>
+        <v>7.422</v>
       </c>
       <c r="M17" t="n">
-        <v>-13.397</v>
+        <v>-45.1297</v>
       </c>
       <c r="N17" t="n">
-        <v>-7.3232</v>
+        <v>-28.5235</v>
       </c>
       <c r="O17" t="n">
-        <v>-6.0736</v>
+        <v>-16.6059</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1489</v>
+        <v>5.2741</v>
       </c>
       <c r="Q17" t="n">
-        <v>-11.9158</v>
+        <v>-35.1616</v>
       </c>
       <c r="R17" t="n">
-        <v>14.0647</v>
+        <v>40.436</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1054</v>
+        <v>9.239800000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8039</v>
+        <v>7.658799999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6983</v>
+        <v>1.5814</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1096999999999997</v>
+        <v>-1.6181</v>
       </c>
       <c r="W17" t="n">
-        <v>6.096</v>
+        <v>2.3973</v>
       </c>
       <c r="X17" t="n">
-        <v>-6.2057</v>
+        <v>-4.015099999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D18" t="n">
-        <v>-15.2861</v>
+        <v>-9.250999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-6.618200000000001</v>
+        <v>-12.4338</v>
       </c>
       <c r="F18" t="n">
-        <v>-8.668000000000001</v>
+        <v>3.183</v>
       </c>
       <c r="G18" t="n">
-        <v>-14.3432</v>
+        <v>-2.061000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-7.9177</v>
+        <v>-4.9538</v>
       </c>
       <c r="I18" t="n">
-        <v>-6.4253</v>
+        <v>2.893</v>
       </c>
       <c r="J18" t="n">
-        <v>4.3995</v>
+        <v>5.4838</v>
       </c>
       <c r="K18" t="n">
-        <v>8.387</v>
+        <v>2.4491</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.9872</v>
+        <v>3.0348</v>
       </c>
       <c r="M18" t="n">
-        <v>-18.7429</v>
+        <v>-7.5449</v>
       </c>
       <c r="N18" t="n">
-        <v>-16.3048</v>
+        <v>-7.403</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.437999999999999</v>
+        <v>-0.1420999999999997</v>
       </c>
       <c r="P18" t="n">
-        <v>12.1111</v>
+        <v>2.5392</v>
       </c>
       <c r="Q18" t="n">
-        <v>-8.7904</v>
+        <v>-16.7993</v>
       </c>
       <c r="R18" t="n">
-        <v>20.9016</v>
+        <v>19.3388</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.7508</v>
+        <v>1.4025</v>
       </c>
       <c r="T18" t="n">
-        <v>-2.2853</v>
+        <v>1.7545</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4655</v>
+        <v>-0.3522</v>
       </c>
       <c r="V18" t="n">
-        <v>-10.3035</v>
+        <v>-11.1321</v>
       </c>
       <c r="W18" t="n">
-        <v>0.05759999999999982</v>
+        <v>-2.8732</v>
       </c>
       <c r="X18" t="n">
-        <v>-10.3612</v>
+        <v>-8.2591</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>Q. ROIG GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>-31.021</v>
+        <v>-12.0611</v>
       </c>
       <c r="E19" t="n">
-        <v>-20.8906</v>
+        <v>-5.824800000000002</v>
       </c>
       <c r="F19" t="n">
-        <v>-10.1306</v>
+        <v>-6.2364</v>
       </c>
       <c r="G19" t="n">
-        <v>-41.5021</v>
+        <v>-15.2057</v>
       </c>
       <c r="H19" t="n">
-        <v>-14.7877</v>
+        <v>-6.1851</v>
       </c>
       <c r="I19" t="n">
-        <v>-26.7135</v>
+        <v>-9.0207</v>
       </c>
       <c r="J19" t="n">
-        <v>-7.662</v>
+        <v>-1.8089</v>
       </c>
       <c r="K19" t="n">
-        <v>11.0766</v>
+        <v>1.1381</v>
       </c>
       <c r="L19" t="n">
-        <v>-18.7387</v>
+        <v>-2.9471</v>
       </c>
       <c r="M19" t="n">
-        <v>-33.8401</v>
+        <v>-13.397</v>
       </c>
       <c r="N19" t="n">
-        <v>-25.8647</v>
+        <v>-7.3232</v>
       </c>
       <c r="O19" t="n">
-        <v>-7.9753</v>
+        <v>-6.0736</v>
       </c>
       <c r="P19" t="n">
-        <v>-6.641500000000001</v>
+        <v>2.1489</v>
       </c>
       <c r="Q19" t="n">
-        <v>-47.8588</v>
+        <v>-11.9158</v>
       </c>
       <c r="R19" t="n">
-        <v>41.2174</v>
+        <v>14.0647</v>
       </c>
       <c r="S19" t="n">
-        <v>-4.6473</v>
+        <v>1.1054</v>
       </c>
       <c r="T19" t="n">
-        <v>-2.3882</v>
+        <v>1.8039</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.2591</v>
+        <v>-0.6983</v>
       </c>
       <c r="V19" t="n">
-        <v>21.7698</v>
+        <v>-0.1096999999999997</v>
       </c>
       <c r="W19" t="n">
-        <v>37.0185</v>
+        <v>6.096</v>
       </c>
       <c r="X19" t="n">
-        <v>-15.2482</v>
+        <v>-6.2057</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>P. CAMPANA SOLER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>-37.1445</v>
+        <v>-15.9292</v>
       </c>
       <c r="E20" t="n">
-        <v>-19.256</v>
+        <v>-15.3806</v>
       </c>
       <c r="F20" t="n">
-        <v>-17.8887</v>
+        <v>-0.5486000000000004</v>
       </c>
       <c r="G20" t="n">
-        <v>-20.7016</v>
+        <v>-30.739</v>
       </c>
       <c r="H20" t="n">
-        <v>-8.362500000000001</v>
+        <v>-16.3164</v>
       </c>
       <c r="I20" t="n">
-        <v>-12.3391</v>
+        <v>-14.4224</v>
       </c>
       <c r="J20" t="n">
-        <v>9.909099999999999</v>
+        <v>-4.868400000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>11.1724</v>
+        <v>5.3565</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2633</v>
+        <v>-10.2246</v>
       </c>
       <c r="M20" t="n">
-        <v>-30.6107</v>
+        <v>-25.8705</v>
       </c>
       <c r="N20" t="n">
-        <v>-19.5351</v>
+        <v>-21.6727</v>
       </c>
       <c r="O20" t="n">
-        <v>-11.0761</v>
+        <v>-4.1975</v>
       </c>
       <c r="P20" t="n">
-        <v>-4.2974</v>
+        <v>4.492999999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>-37.1148</v>
+        <v>-41.0218</v>
       </c>
       <c r="R20" t="n">
-        <v>32.8177</v>
+        <v>45.5149</v>
       </c>
       <c r="S20" t="n">
-        <v>-3.0054</v>
+        <v>3.0847</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.7474</v>
+        <v>2.4755</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.2577</v>
+        <v>0.6091999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>-9.1401</v>
+        <v>7.231899999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>9.697100000000001</v>
+        <v>28.0344</v>
       </c>
       <c r="X20" t="n">
-        <v>-18.8373</v>
+        <v>-20.8022</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,66 +2047,300 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>-63.5635</v>
+        <v>-16.8211</v>
       </c>
       <c r="E21" t="n">
-        <v>-31.9255</v>
+        <v>-8.1531</v>
       </c>
       <c r="F21" t="n">
+        <v>-8.668000000000001</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-15.8782</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-9.4526</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-6.4253</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.8647</v>
+      </c>
+      <c r="K21" t="n">
+        <v>6.852</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-3.9872</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-18.7429</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-16.3048</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-2.437999999999999</v>
+      </c>
+      <c r="P21" t="n">
+        <v>12.1111</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-8.7904</v>
+      </c>
+      <c r="R21" t="n">
+        <v>20.9016</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-2.7508</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-2.2853</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.4655</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-10.3035</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.05759999999999982</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-10.3612</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A. BARQUETS ARIZA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>26</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-31.021</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-20.8906</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-10.1306</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-41.5021</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-14.7877</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-26.7135</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-7.662</v>
+      </c>
+      <c r="K22" t="n">
+        <v>11.0766</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-18.7387</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-33.8401</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-25.8647</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-7.9753</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-6.641500000000001</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-47.8588</v>
+      </c>
+      <c r="R22" t="n">
+        <v>41.2174</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-4.6473</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-2.3882</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-2.2591</v>
+      </c>
+      <c r="V22" t="n">
+        <v>21.7698</v>
+      </c>
+      <c r="W22" t="n">
+        <v>37.0185</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-15.2482</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>D. ROY CARNICER</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>26</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-37.1445</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-19.256</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-17.8887</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-20.7016</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-8.362500000000001</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-12.3391</v>
+      </c>
+      <c r="J23" t="n">
+        <v>9.909099999999999</v>
+      </c>
+      <c r="K23" t="n">
+        <v>11.1724</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-1.2633</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-30.6107</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-19.5351</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-11.0761</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-4.2974</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-37.1148</v>
+      </c>
+      <c r="R23" t="n">
+        <v>32.8177</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-3.0054</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-1.7474</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-1.2577</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-9.1401</v>
+      </c>
+      <c r="W23" t="n">
+        <v>9.697100000000001</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-18.8373</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>26</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-63.5626</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-31.9246</v>
+      </c>
+      <c r="F24" t="n">
         <v>-31.6384</v>
       </c>
-      <c r="G21" t="n">
-        <v>-150.2493</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-68.62700000000001</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-81.6216</v>
-      </c>
-      <c r="J21" t="n">
-        <v>141.4188</v>
-      </c>
-      <c r="K21" t="n">
-        <v>140.6027</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.8165999999999987</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="G24" t="n">
+        <v>-150.2489</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-68.6264</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-81.62130000000001</v>
+      </c>
+      <c r="J24" t="n">
+        <v>141.4199</v>
+      </c>
+      <c r="K24" t="n">
+        <v>140.6031</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.8173999999999968</v>
+      </c>
+      <c r="M24" t="n">
         <v>-291.6691</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N24" t="n">
         <v>-209.2306</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O24" t="n">
         <v>-82.4391</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P24" t="n">
         <v>46.8823</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q24" t="n">
         <v>-347.7083</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R24" t="n">
         <v>394.5923</v>
       </c>
-      <c r="S21" t="n">
-        <v>8.755199999999997</v>
-      </c>
-      <c r="T21" t="n">
-        <v>6.7238</v>
-      </c>
-      <c r="U21" t="n">
+      <c r="S24" t="n">
+        <v>8.755200000000004</v>
+      </c>
+      <c r="T24" t="n">
+        <v>6.723800000000002</v>
+      </c>
+      <c r="U24" t="n">
         <v>2.032299999999999</v>
       </c>
-      <c r="V21" t="n">
+      <c r="V24" t="n">
         <v>31.047</v>
       </c>
-      <c r="W21" t="n">
+      <c r="W24" t="n">
         <v>167.6404</v>
       </c>
-      <c r="X21" t="n">
+      <c r="X24" t="n">
         <v>-136.5926</v>
       </c>
     </row>
